--- a/Grids Germany/No leap years/Saxony insights/[Saxony][Euclidean][Raw]Aggregated_U_test.xlsx
+++ b/Grids Germany/No leap years/Saxony insights/[Saxony][Euclidean][Raw]Aggregated_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_P2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SD_P1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SD_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Median_P1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Median_P2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Median_difference_P2_minus_P1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -495,40 +507,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1410</v>
+        <v>1380</v>
       </c>
       <c r="C2" t="n">
         <v>420</v>
       </c>
       <c r="D2" t="n">
-        <v>10.78337564866108</v>
+        <v>11.1152778795762</v>
       </c>
       <c r="E2" t="n">
-        <v>12.2657999175524</v>
+        <v>12.26532367538367</v>
       </c>
       <c r="F2" t="n">
-        <v>4.309825504375554</v>
+        <v>4.279372109678623</v>
       </c>
       <c r="G2" t="n">
-        <v>3.130484395771349</v>
+        <v>3.115939713427499</v>
       </c>
       <c r="H2" t="n">
-        <v>10.8040448367681</v>
+        <v>11.28298108333225</v>
       </c>
       <c r="I2" t="n">
-        <v>11.93375641291675</v>
+        <v>11.87571043504035</v>
       </c>
       <c r="J2" t="n">
-        <v>1.129711576148651</v>
+        <v>0.5927293517081011</v>
       </c>
       <c r="K2" t="n">
-        <v>236820</v>
+        <v>246841</v>
       </c>
       <c r="L2" t="n">
-        <v>4.484616983688046e-10</v>
+        <v>4.105981838169627e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.793846793475219e-09</v>
+        <v>1.642392735267851e-05</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -541,40 +553,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1410</v>
+        <v>1380</v>
       </c>
       <c r="C3" t="n">
         <v>420</v>
       </c>
       <c r="D3" t="n">
-        <v>70.06057570267788</v>
+        <v>70.07000820116583</v>
       </c>
       <c r="E3" t="n">
-        <v>79.21656416527743</v>
+        <v>79.22411173537202</v>
       </c>
       <c r="F3" t="n">
-        <v>11.35652009636077</v>
+        <v>11.39452757774548</v>
       </c>
       <c r="G3" t="n">
-        <v>8.270312187988115</v>
+        <v>8.287825013520704</v>
       </c>
       <c r="H3" t="n">
-        <v>69.99953205586975</v>
+        <v>70.05009863654084</v>
       </c>
       <c r="I3" t="n">
         <v>79.73920634977685</v>
       </c>
       <c r="J3" t="n">
-        <v>9.7396742939071</v>
+        <v>9.689107713236012</v>
       </c>
       <c r="K3" t="n">
-        <v>154151</v>
+        <v>151140</v>
       </c>
       <c r="L3" t="n">
-        <v>2.014311030479891e-50</v>
+        <v>5.409267005782361e-50</v>
       </c>
       <c r="M3" t="n">
-        <v>8.057244121919565e-50</v>
+        <v>2.163706802312944e-49</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -587,43 +599,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1410</v>
+        <v>1380</v>
       </c>
       <c r="C4" t="n">
         <v>420</v>
       </c>
       <c r="D4" t="n">
-        <v>13.23576206350402</v>
+        <v>13.67161623962217</v>
       </c>
       <c r="E4" t="n">
-        <v>13.92767637135523</v>
+        <v>13.90767583431183</v>
       </c>
       <c r="F4" t="n">
-        <v>4.165761423401584</v>
+        <v>4.126617107028816</v>
       </c>
       <c r="G4" t="n">
-        <v>2.638220292100501</v>
+        <v>2.657471677907125</v>
       </c>
       <c r="H4" t="n">
-        <v>13.58728150342735</v>
+        <v>13.89121650938275</v>
       </c>
       <c r="I4" t="n">
         <v>13.7114491810391</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1241676776117497</v>
+        <v>-0.1797673283436509</v>
       </c>
       <c r="K4" t="n">
-        <v>270978.5</v>
+        <v>286810.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0082245940282879</v>
+        <v>0.7486075309910769</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0328983761131516</v>
+        <v>1</v>
       </c>
       <c r="N4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -633,40 +645,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1410</v>
+        <v>1380</v>
       </c>
       <c r="C5" t="n">
         <v>420</v>
       </c>
       <c r="D5" t="n">
-        <v>88.76836938450617</v>
+        <v>88.34156425749742</v>
       </c>
       <c r="E5" t="n">
-        <v>76.84079136845779</v>
+        <v>76.99989827881321</v>
       </c>
       <c r="F5" t="n">
-        <v>22.12793729365899</v>
+        <v>22.2852176742045</v>
       </c>
       <c r="G5" t="n">
-        <v>30.77366389370666</v>
+        <v>30.59952091800777</v>
       </c>
       <c r="H5" t="n">
-        <v>90.21338805547691</v>
+        <v>89.92995471270871</v>
       </c>
       <c r="I5" t="n">
-        <v>79.12427681856781</v>
+        <v>79.80439003679585</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.0891112369091</v>
+        <v>-10.12556467591286</v>
       </c>
       <c r="K5" t="n">
-        <v>359343</v>
+        <v>348365</v>
       </c>
       <c r="L5" t="n">
-        <v>2.870659201682074e-11</v>
+        <v>3.403290138053726e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>1.14826368067283e-10</v>
+        <v>1.36131605522149e-09</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
